--- a/data/trans_dic/P25C$otraforma_2023-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P25C$otraforma_2023-Provincia-trans_dic.xlsx
@@ -490,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población cuyo método para dejar de fumar fue otro</t>
+          <t>Población cuyo método para dejar de fumar fue otro (tasa de respuesta: 99,69%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0; 2,99</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0; 7,32</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0; 2,15</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>11,04; 26,18</t>
+          <t>10,35; 24,47</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,2; 10,71</t>
+          <t>1,15; 11,24</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>7,7; 17,86</t>
+          <t>7,99; 17,61</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,85</t>
+          <t>0,9; 11,2</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,4</t>
+          <t>0,0; 7,64</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,01; 7,38</t>
+          <t>1,09; 7,9</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0; 1,67</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,23</t>
+          <t>0,0; 6,18</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,71</t>
+          <t>0,0; 1,88</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0; 7,06</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0; 9,05</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0; 4,07</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 2,42</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0; 9,05</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0; 1,94</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,75</t>
+          <t>0,0; 3,95</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>2,01; 8,98</t>
+          <t>1,94; 9,12</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1,18; 4,71</t>
+          <t>1,13; 4,5</t>
         </is>
       </c>
     </row>
@@ -922,17 +922,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,64</t>
+          <t>0,0; 2,67</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,33</t>
+          <t>0,0; 9,39</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,4</t>
+          <t>0,0; 2,6</t>
         </is>
       </c>
     </row>
@@ -972,17 +972,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>1,0; 4,69</t>
+          <t>0,96; 4,83</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>1,57; 4,69</t>
+          <t>1,57; 4,48</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1,42; 4,05</t>
+          <t>1,48; 4,18</t>
         </is>
       </c>
     </row>
@@ -1029,7 +1029,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población cuyo método para dejar de fumar fue otro</t>
+          <t>Población cuyo método para dejar de fumar fue otro (tasa de respuesta: 99,69%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1134,17 +1134,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 1422</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 885</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 1284</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -1207,17 +1207,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>12197; 28927</t>
+          <t>11435; 27043</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>785; 7010</t>
+          <t>754; 7355</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>13554; 31427</t>
+          <t>14053; 30994</t>
         </is>
       </c>
     </row>
@@ -1280,17 +1280,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 8146</t>
+          <t>619; 7698</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 3661</t>
+          <t>0; 3779</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1193; 8728</t>
+          <t>1289; 9342</t>
         </is>
       </c>
     </row>
@@ -1353,17 +1353,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 1575</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0; 3628</t>
+          <t>0; 3599</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0; 4143</t>
+          <t>0; 2869</t>
         </is>
       </c>
     </row>
@@ -1426,17 +1426,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0; 1045</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>0; 753</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>0; 941</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -1499,17 +1499,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0; 1100</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0; 997</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0; 1092</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -1572,17 +1572,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>0; 3345</t>
+          <t>0; 4806</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>1907; 8519</t>
+          <t>1835; 8651</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>2552; 10214</t>
+          <t>2447; 9744</t>
         </is>
       </c>
     </row>
@@ -1645,17 +1645,17 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>0; 9147</t>
+          <t>0; 9238</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>0; 3552</t>
+          <t>0; 3573</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>0; 9206</t>
+          <t>0; 10010</t>
         </is>
       </c>
     </row>
@@ -1718,17 +1718,17 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>8461; 39834</t>
+          <t>8153; 40995</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>5309; 15816</t>
+          <t>5282; 15108</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>16853; 48026</t>
+          <t>17537; 49645</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P25C$otraforma_2023-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P25C$otraforma_2023-Provincia-trans_dic.xlsx
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>17,15%</t>
+          <t>18,63%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>4,32%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>12,43%</t>
+          <t>13,48%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>10,35; 24,47</t>
+          <t>12,45; 26,94</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,15; 11,24</t>
+          <t>1,43; 11,13</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>7,99; 17,61</t>
+          <t>8,95; 19,12</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>4,07%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>2,93%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,9; 11,2</t>
+          <t>1,29; 12,35</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,64</t>
+          <t>0,0; 6,97</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,09; 7,9</t>
+          <t>1,04; 7,18</t>
         </is>
       </c>
     </row>
@@ -704,12 +704,12 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,42%</t>
         </is>
       </c>
     </row>
@@ -727,12 +727,12 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,18</t>
+          <t>0,0; 6,7</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,88</t>
+          <t>0,0; 2,14</t>
         </is>
       </c>
     </row>
@@ -849,17 +849,17 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>4,48%</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,28%</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,95</t>
+          <t>0,0; 3,13</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>1,94; 9,12</t>
+          <t>1,91; 8,49</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1,13; 4,5</t>
+          <t>1,07; 4,3</t>
         </is>
       </c>
     </row>
@@ -899,17 +899,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>1,75%</t>
         </is>
       </c>
     </row>
@@ -922,17 +922,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,67</t>
+          <t>0,0; 6,16</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,39</t>
+          <t>0,0; 8,67</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,6</t>
+          <t>0,49; 4,81</t>
         </is>
       </c>
     </row>
@@ -949,17 +949,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>3,66%</t>
         </is>
       </c>
     </row>
@@ -972,17 +972,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0,96; 4,83</t>
+          <t>2,73; 6,14</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>1,57; 4,48</t>
+          <t>1,45; 4,31</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1,48; 4,18</t>
+          <t>2,66; 4,95</t>
         </is>
       </c>
     </row>
@@ -1184,17 +1184,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>18949</t>
+          <t>22098</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>2917</t>
+          <t>2882</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>21867</t>
+          <t>24980</t>
         </is>
       </c>
     </row>
@@ -1207,17 +1207,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>11435; 27043</t>
+          <t>14763; 31949</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>754; 7355</t>
+          <t>953; 7426</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>14053; 30994</t>
+          <t>16580; 35436</t>
         </is>
       </c>
     </row>
@@ -1257,17 +1257,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2868</t>
+          <t>2757</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>694</t>
+          <t>677</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>3562</t>
+          <t>3434</t>
         </is>
       </c>
     </row>
@@ -1280,17 +1280,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>619; 7698</t>
+          <t>870; 8361</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 3779</t>
+          <t>0; 3461</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1289; 9342</t>
+          <t>1225; 8422</t>
         </is>
       </c>
     </row>
@@ -1335,12 +1335,12 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>704</t>
+          <t>731</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>704</t>
+          <t>731</t>
         </is>
       </c>
     </row>
@@ -1358,12 +1358,12 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0; 3599</t>
+          <t>0; 4361</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0; 2869</t>
+          <t>0; 3688</t>
         </is>
       </c>
     </row>
@@ -1549,17 +1549,17 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>718</t>
+          <t>871</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>4455</t>
+          <t>4817</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>5173</t>
+          <t>5688</t>
         </is>
       </c>
     </row>
@@ -1572,17 +1572,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>0; 4806</t>
+          <t>0; 4460</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>1835; 8651</t>
+          <t>2056; 9123</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>2447; 9744</t>
+          <t>2684; 10748</t>
         </is>
       </c>
     </row>
@@ -1622,17 +1622,17 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>1761</t>
+          <t>1979</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>697</t>
+          <t>781</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2458</t>
+          <t>2760</t>
         </is>
       </c>
     </row>
@@ -1645,17 +1645,17 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>0; 9238</t>
+          <t>0; 6997</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>0; 3573</t>
+          <t>0; 3836</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>0; 10010</t>
+          <t>777; 7587</t>
         </is>
       </c>
     </row>
@@ -1695,17 +1695,17 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>24296</t>
+          <t>27705</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>9467</t>
+          <t>9888</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>33763</t>
+          <t>37593</t>
         </is>
       </c>
     </row>
@@ -1718,17 +1718,17 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>8153; 40995</t>
+          <t>18024; 40558</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>5282; 15108</t>
+          <t>5310; 15779</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>17537; 49645</t>
+          <t>27280; 50816</t>
         </is>
       </c>
     </row>
